--- a/Result/profitability/2038.xlsx
+++ b/Result/profitability/2038.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.10125</v>
+        <v>0.09625</v>
       </c>
       <c r="N2" t="n">
-        <v>2.525</v>
+        <v>2.315</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.88</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4725</v>
+        <v>0.45625</v>
       </c>
       <c r="N3" t="n">
-        <v>3.59</v>
+        <v>3.5025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.91</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5862499999999999</v>
+        <v>0.5237499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>4.09875</v>
+        <v>3.7425</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3487499999999999</v>
+        <v>0.35</v>
       </c>
       <c r="N5" t="n">
-        <v>2.88375</v>
+        <v>2.68125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2775</v>
+        <v>0.305</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05875</v>
+        <v>2.34375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.27</v>
+        <v>0.30875</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4875</v>
+        <v>2.67875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3175</v>
+        <v>0.28125</v>
       </c>
       <c r="N8" t="n">
-        <v>2.795</v>
+        <v>2.66875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.02</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.09750000000000003</v>
+        <v>-0.09749999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>1.32125</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2046</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E75" t="n">
+        <v>18</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.0775</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.39625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.8125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.531578947368421</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.07142857142857151</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6454183266932271</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
